--- a/data/horarios-141-2026-10-07.xlsx
+++ b/data/horarios-141-2026-10-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:01:34</t>
+          <t>Última actualización: 20:34:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 21</t>
+          <t>Total filas: 37</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1029,422 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>19</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>19</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>32</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>39</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>45</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>46</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>47</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>57</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>59</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>62</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>78</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>95</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1041,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,14 +1470,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:01:34</t>
+          <t>Última actualización: 20:34:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -1122,6 +1538,32 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20:34:05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1134,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,14 +1589,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:01:34</t>
+          <t>Última actualización: 20:34:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -1293,6 +1735,84 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20:34:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20:34:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>84</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20:34:45</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
